--- a/sal-updated/rawDataset_SAL.xlsx
+++ b/sal-updated/rawDataset_SAL.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,11 +523,6 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
@@ -544,6 +539,310 @@
       </c>
       <c r="J3" t="n">
         <v>1067</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>45807.53665129629</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>33dffdsd</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>7878-4324_234324-3434</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>34</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>10.76500013819467</v>
+      </c>
+      <c r="I4" t="n">
+        <v>58.0783053</v>
+      </c>
+      <c r="J4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="b">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>45807.53758841435</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>33dffdsd</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>7878-4324_234324-3434</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>34</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>10.76500013819467</v>
+      </c>
+      <c r="I5" t="n">
+        <v>58.0783053</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>45807.53764806713</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>33dffdsd</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>7878-4324_234324-3434</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>34</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>10.76500013819467</v>
+      </c>
+      <c r="I6" t="n">
+        <v>58.0783053</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="b">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>45807.53774239583</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>33dffdsd</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7878-4324_234324-3434</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>34</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>10.76500013819467</v>
+      </c>
+      <c r="I7" t="n">
+        <v>58.0783053</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="b">
+        <v>1</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>45807.53781646991</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33dffdsd</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>7878-4324_234324-3434</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>34</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>10.76500013819467</v>
+      </c>
+      <c r="I8" t="n">
+        <v>58.0783053</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="b">
+        <v>1</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>45807.53785234954</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>33dffdsd</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7878-4324_234324-3434</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>34</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>10.76500013819467</v>
+      </c>
+      <c r="I9" t="n">
+        <v>58.0783053</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>45807.53790443287</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>33dffdsd</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7878-4324_234324-3434</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>34</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>10.76500013819467</v>
+      </c>
+      <c r="I10" t="n">
+        <v>58.0783053</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="b">
+        <v>1</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>45807.53793043982</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>33dffdsd</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>7878-4324_234324-3434</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>34</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>-99.19999489561776</v>
+      </c>
+      <c r="I11" t="n">
+        <v>55.38361290000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -557,7 +856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,11 +966,6 @@
       <c r="C3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
@@ -695,6 +989,366 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>45807.53665129629</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>33dffdsd</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>7878-4324_234324-3434</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>34</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>45807.53758841435</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>33dffdsd</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7878-4324_234324-3434</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>34</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1211</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>45807.53764806713</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>33dffdsd</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7878-4324_234324-3434</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>34</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>45807.53774239583</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>33dffdsd</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>7878-4324_234324-3434</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>34</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>45807.53781646991</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>33dffdsd</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>7878-4324_234324-3434</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>34</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2232</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>45807.53785234954</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>33dffdsd</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>12</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>7878-4324_234324-3434</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>34</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2232</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>45807.53790443287</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>33dffdsd</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>7878-4324_234324-3434</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>34</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>32323</v>
+      </c>
+      <c r="H10" t="n">
+        <v>32323</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2232</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>45807.53793043982</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>33dffdsd</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>7878-4324_234324-3434</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>34</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>32323</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>32323</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>100</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -709,7 +1363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,17 +1452,13 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>45805.60530759155</v>
+        <v>45805.6053075926</v>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>0</v>
       </c>
@@ -826,6 +1476,286 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>45807.53665129629</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>33dffdsd</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>7878-4324_234324-3434</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>34</v>
+      </c>
+      <c r="F4" t="n">
+        <v>57.37722320000001</v>
+      </c>
+      <c r="G4" t="n">
+        <v>59.56591380000003</v>
+      </c>
+      <c r="H4" t="n">
+        <v>59.61454549999999</v>
+      </c>
+      <c r="I4" t="n">
+        <v>59.18536919999999</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>45807.53758841435</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>33dffdsd</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7878-4324_234324-3434</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>34</v>
+      </c>
+      <c r="F5" t="n">
+        <v>57.37722320000001</v>
+      </c>
+      <c r="G5" t="n">
+        <v>59.56591380000003</v>
+      </c>
+      <c r="H5" t="n">
+        <v>59.61454549999999</v>
+      </c>
+      <c r="I5" t="n">
+        <v>59.18536919999999</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>45807.53764806713</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>33dffdsd</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7878-4324_234324-3434</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>34</v>
+      </c>
+      <c r="F6" t="n">
+        <v>57.37722320000001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>59.56591380000003</v>
+      </c>
+      <c r="H6" t="n">
+        <v>59.61454549999999</v>
+      </c>
+      <c r="I6" t="n">
+        <v>59.18536919999999</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>45807.53774239583</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>33dffdsd</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>7878-4324_234324-3434</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>34</v>
+      </c>
+      <c r="F7" t="n">
+        <v>57.37722320000001</v>
+      </c>
+      <c r="G7" t="n">
+        <v>59.56591380000003</v>
+      </c>
+      <c r="H7" t="n">
+        <v>59.61454549999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>59.18536919999999</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>45807.53781646991</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>33dffdsd</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>7878-4324_234324-3434</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>34</v>
+      </c>
+      <c r="F8" t="n">
+        <v>57.37722320000001</v>
+      </c>
+      <c r="G8" t="n">
+        <v>59.56591380000003</v>
+      </c>
+      <c r="H8" t="n">
+        <v>59.61454549999999</v>
+      </c>
+      <c r="I8" t="n">
+        <v>59.18536919999999</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>45807.53785234954</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>33dffdsd</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>12</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>7878-4324_234324-3434</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>34</v>
+      </c>
+      <c r="F9" t="n">
+        <v>57.37722320000001</v>
+      </c>
+      <c r="G9" t="n">
+        <v>59.56591380000003</v>
+      </c>
+      <c r="H9" t="n">
+        <v>59.61454549999999</v>
+      </c>
+      <c r="I9" t="n">
+        <v>59.18536919999999</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>45807.53790443287</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>33dffdsd</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>7878-4324_234324-3434</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>34</v>
+      </c>
+      <c r="F10" t="n">
+        <v>57.37722320000001</v>
+      </c>
+      <c r="G10" t="n">
+        <v>59.56591380000003</v>
+      </c>
+      <c r="H10" t="n">
+        <v>59.61454549999999</v>
+      </c>
+      <c r="I10" t="n">
+        <v>59.18536919999999</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>45807.53793043403</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>33dffdsd</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>7878-4324_234324-3434</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>34</v>
+      </c>
+      <c r="F11" t="n">
+        <v>57.37722320000001</v>
+      </c>
+      <c r="G11" t="n">
+        <v>59.56591380000003</v>
+      </c>
+      <c r="H11" t="n">
+        <v>59.61454549999999</v>
+      </c>
+      <c r="I11" t="n">
+        <v>59.18536919999999</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/sal-updated/rawDataset_SAL.xlsx
+++ b/sal-updated/rawDataset_SAL.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,6 +843,72 @@
       </c>
       <c r="J11" t="n">
         <v>100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="b">
+        <v>1</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>45811.51889208333</v>
+      </c>
+      <c r="D12" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>N/A-N/A_0.0-0.1</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>100.50 (within Buffer)</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>60.30240219510276</v>
+      </c>
+      <c r="I12" t="n">
+        <v>58.6591565</v>
+      </c>
+      <c r="J12" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="b">
+        <v>1</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>45811.51958800926</v>
+      </c>
+      <c r="D13" t="n">
+        <v>11</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>M.C.</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>60.30240219510276</v>
+      </c>
+      <c r="I13" t="n">
+        <v>58.6591565</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1010</v>
       </c>
     </row>
   </sheetData>
@@ -856,7 +922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1324,15 +1390,11 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>32323</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>32323</t>
-        </is>
+      <c r="G11" t="n">
+        <v>32323</v>
+      </c>
+      <c r="H11" t="n">
+        <v>32323</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
@@ -1347,6 +1409,92 @@
         <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>45811.51889208333</v>
+      </c>
+      <c r="C12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>N/A-N/A_0.0-0.1</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>100</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>45811.51958800926</v>
+      </c>
+      <c r="C13" t="n">
+        <v>11</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1010</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1363,7 +1511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1724,7 +1872,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>45807.53793043403</v>
+        <v>45807.53793043982</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1756,6 +1904,68 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>45811.51889208333</v>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>N/A-N/A_0.0-0.1</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>57.37722320000001</v>
+      </c>
+      <c r="G12" t="n">
+        <v>59.56591380000003</v>
+      </c>
+      <c r="H12" t="n">
+        <v>59.61454549999999</v>
+      </c>
+      <c r="I12" t="n">
+        <v>59.18536919999999</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>45811.51958800408</v>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="n">
+        <v>11</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>57.37722320000001</v>
+      </c>
+      <c r="G13" t="n">
+        <v>59.56591380000003</v>
+      </c>
+      <c r="H13" t="n">
+        <v>59.61454549999999</v>
+      </c>
+      <c r="I13" t="n">
+        <v>59.18536919999999</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/sal-updated/rawDataset_SAL.xlsx
+++ b/sal-updated/rawDataset_SAL.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,32 +492,24 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>45811.97956070602</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Yassin-test</t>
-        </is>
+        <v>45817.56536278936</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>N/A-N/A_0.0-0.1</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G2" t="n">
-        <v>170.98</v>
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
       </c>
       <c r="H2" t="n">
-        <v>170.9761228361776</v>
+        <v>-87.66663467222415</v>
       </c>
       <c r="I2" t="n">
-        <v>57.3603937</v>
+        <v>56.47996450000001</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
@@ -528,23 +520,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>45811.9803328125</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Yassin-test</t>
-        </is>
+        <v>45817.56593384259</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>3232-323233_11.0-12.1</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -552,10 +534,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-82.22042600002388</v>
+        <v>-87.66663467222415</v>
       </c>
       <c r="I3" t="n">
-        <v>55.32598380000001</v>
+        <v>56.47996450000001</v>
       </c>
       <c r="J3" t="n">
         <v>100</v>
@@ -566,23 +548,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>45811.98120413195</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Yassin-test</t>
-        </is>
+        <v>45817.56596280092</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3232-323233_11.0-12.1</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -590,10 +562,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-82.22042600002388</v>
+        <v>-87.66663467222415</v>
       </c>
       <c r="I4" t="n">
-        <v>55.32598380000001</v>
+        <v>56.47996450000001</v>
       </c>
       <c r="J4" t="n">
         <v>100</v>
@@ -604,23 +576,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>45811.9812369213</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Yassin-test</t>
-        </is>
+        <v>45817.56734314815</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3232-323233_11.0-12.1</t>
-        </is>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -628,10 +590,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-82.22042600002388</v>
+        <v>-98.35605885410388</v>
       </c>
       <c r="I5" t="n">
-        <v>55.32598380000001</v>
+        <v>55.55224</v>
       </c>
       <c r="J5" t="n">
         <v>100</v>
@@ -642,21 +604,11 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>45811.98418329861</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3434</t>
-        </is>
+        <v>45817.56782914352</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>213123232-34243244_0.0-0.1</t>
-        </is>
-      </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
@@ -666,13 +618,102 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-64.42628657361558</v>
+        <v>-98.35605885410388</v>
       </c>
       <c r="I6" t="n">
-        <v>56.36164619999999</v>
+        <v>55.55224</v>
       </c>
       <c r="J6" t="n">
-        <v>100</v>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="b">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>45817.56814799768</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>-98.35605885410388</v>
+      </c>
+      <c r="I7" t="n">
+        <v>55.55224</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="b">
+        <v>1</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>45817.56861430556</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>-98.35605885410388</v>
+      </c>
+      <c r="I8" t="n">
+        <v>55.55224</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="b">
+        <v>1</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>45817.56871664352</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>-98.35605885410388</v>
+      </c>
+      <c r="I9" t="n">
+        <v>55.55224</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -686,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -758,23 +799,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>45811.97956070602</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Yassin-test</t>
-        </is>
+        <v>45817.56536278936</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>N/A-N/A_0.0-0.1</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -791,7 +822,7 @@
         <v>0.2</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -801,23 +832,13 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>45811.9803328125</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Yassin-test</t>
-        </is>
+        <v>45817.56593384259</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>3232-323233_11.0-12.1</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +855,7 @@
         <v>0.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -844,23 +865,13 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>45811.98120413195</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Yassin-test</t>
-        </is>
+        <v>45817.56596280092</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>3232-323233_11.0-12.1</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -877,7 +888,7 @@
         <v>0.2</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -887,23 +898,13 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>45811.9812369213</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Yassin-test</t>
-        </is>
+        <v>45817.56734314815</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>3232-323233_11.0-12.1</t>
-        </is>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -920,7 +921,7 @@
         <v>0.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -930,21 +931,11 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>45811.98418329861</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3434</t>
-        </is>
+        <v>45817.56782914352</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>213123232-34243244_0.0-0.1</t>
-        </is>
-      </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
@@ -953,18 +944,8 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>100</v>
+        <v>5000</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -973,9 +954,129 @@
         <v>0.2</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>45817.56814799768</v>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>120</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>45817.56861430556</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>3232</v>
+      </c>
+      <c r="H8" t="n">
+        <v>35545454656</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>120</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>45817.56871664352</v>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3232</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>35545454656</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>120</v>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -992,7 +1093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1054,194 +1155,223 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>45811.97956070602</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Yassin-test</t>
-        </is>
-      </c>
+        <v>45817.56536278936</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>N/A-N/A_0.0-0.1</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>55.31438920000001</v>
+        <v>56.80026</v>
       </c>
       <c r="G2" t="n">
-        <v>57.51581460000001</v>
+        <v>57.29622609999999</v>
       </c>
       <c r="H2" t="n">
-        <v>59.49700910000001</v>
+        <v>57.97749800000003</v>
       </c>
       <c r="I2" t="n">
-        <v>59.12874810000002</v>
-      </c>
-      <c r="J2" t="n">
-        <v>732.7348883729181</v>
-      </c>
-      <c r="K2" t="n">
-        <v>58.6210053</v>
-      </c>
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>45811.9803328125</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Yassin-test</t>
-        </is>
-      </c>
+        <v>45817.56593384259</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>11</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>3232-323233_11.0-12.1</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>55.31438920000001</v>
+        <v>56.80026</v>
       </c>
       <c r="G3" t="n">
-        <v>57.51581460000001</v>
+        <v>57.29622609999999</v>
       </c>
       <c r="H3" t="n">
-        <v>59.49700910000001</v>
+        <v>57.97749800000003</v>
       </c>
       <c r="I3" t="n">
-        <v>59.12874810000002</v>
-      </c>
-      <c r="J3" t="n">
-        <v>732.7348883729181</v>
-      </c>
-      <c r="K3" t="n">
-        <v>58.6210053</v>
-      </c>
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>45811.98120413195</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Yassin-test</t>
-        </is>
-      </c>
+        <v>45817.56596280092</v>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>11</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>3232-323233_11.0-12.1</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>55.31438920000001</v>
+        <v>56.80026</v>
       </c>
       <c r="G4" t="n">
-        <v>57.51581460000001</v>
+        <v>57.29622609999999</v>
       </c>
       <c r="H4" t="n">
-        <v>59.49700910000001</v>
+        <v>57.97749800000003</v>
       </c>
       <c r="I4" t="n">
-        <v>59.12874810000002</v>
-      </c>
-      <c r="J4" t="n">
-        <v>732.7348883729181</v>
-      </c>
-      <c r="K4" t="n">
-        <v>58.6210053</v>
-      </c>
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>45811.9812369213</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Yassin-test</t>
-        </is>
-      </c>
+        <v>45817.56734314815</v>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>11</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>3232-323233_11.0-12.1</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>55.31438920000001</v>
+        <v>56.80026</v>
       </c>
       <c r="G5" t="n">
-        <v>57.51581460000001</v>
+        <v>57.29622609999999</v>
       </c>
       <c r="H5" t="n">
-        <v>59.49700910000001</v>
+        <v>57.97749800000003</v>
       </c>
       <c r="I5" t="n">
-        <v>59.12874810000002</v>
-      </c>
-      <c r="J5" t="n">
-        <v>732.7348883729181</v>
-      </c>
-      <c r="K5" t="n">
-        <v>58.6210053</v>
-      </c>
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>45811.98418330038</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3434</t>
-        </is>
-      </c>
+        <v>45817.56782914352</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>213123232-34243244_0.0-0.1</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>55.31438920000001</v>
+        <v>56.80026</v>
       </c>
       <c r="G6" t="n">
-        <v>57.51581460000001</v>
+        <v>57.29622609999999</v>
       </c>
       <c r="H6" t="n">
-        <v>59.49700910000001</v>
+        <v>57.97749800000003</v>
       </c>
       <c r="I6" t="n">
-        <v>59.12874810000002</v>
+        <v>59.50070250000001</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>45817.56814799768</v>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G7" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H7" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I7" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>45817.56861430556</v>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G8" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H8" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I8" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>45817.56871664818</v>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G9" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H9" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I9" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/sal-updated/rawDataset_SAL.xlsx
+++ b/sal-updated/rawDataset_SAL.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,11 +693,6 @@
       <c r="D9" t="n">
         <v>8</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
@@ -714,6 +709,767 @@
       </c>
       <c r="J9" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>45818.52019158565</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>-96.11523113886463</v>
+      </c>
+      <c r="I10" t="n">
+        <v>55.9481351</v>
+      </c>
+      <c r="J10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="b">
+        <v>1</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>45818.52070096065</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1603.65</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>962.1880809905001</v>
+      </c>
+      <c r="I11" t="n">
+        <v>58.53123009999999</v>
+      </c>
+      <c r="J11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="b">
+        <v>1</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>45818.52240875</v>
+      </c>
+      <c r="D12" t="n">
+        <v>11</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>326.07</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>195.639485196275</v>
+      </c>
+      <c r="I12" t="n">
+        <v>57.94245370000001</v>
+      </c>
+      <c r="J12" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="b">
+        <v>1</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>45818.52286226852</v>
+      </c>
+      <c r="D13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>326.07</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>195.639485196275</v>
+      </c>
+      <c r="I13" t="n">
+        <v>57.94245370000001</v>
+      </c>
+      <c r="J13" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="b">
+        <v>1</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>45818.52290732639</v>
+      </c>
+      <c r="D14" t="n">
+        <v>13</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>326.07</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>195.639485196275</v>
+      </c>
+      <c r="I14" t="n">
+        <v>57.94245370000001</v>
+      </c>
+      <c r="J14" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="b">
+        <v>1</v>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>45818.52301774306</v>
+      </c>
+      <c r="D15" t="n">
+        <v>14</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>M.C.</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>195.639485196275</v>
+      </c>
+      <c r="I15" t="n">
+        <v>57.94245370000001</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="b">
+        <v>1</v>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>45818.52323211805</v>
+      </c>
+      <c r="D16" t="n">
+        <v>15</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>326.07</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>195.639485196275</v>
+      </c>
+      <c r="I16" t="n">
+        <v>57.94245370000001</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="b">
+        <v>1</v>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>45818.53143945602</v>
+      </c>
+      <c r="D17" t="n">
+        <v>16</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>-83.34669394459019</v>
+      </c>
+      <c r="I17" t="n">
+        <v>56.6182111</v>
+      </c>
+      <c r="J17" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="b">
+        <v>1</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>45818.54859282407</v>
+      </c>
+      <c r="D18" t="n">
+        <v>17</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>-96.05763562375152</v>
+      </c>
+      <c r="I18" t="n">
+        <v>55.95491030000001</v>
+      </c>
+      <c r="J18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="b">
+        <v>1</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>45818.54947380787</v>
+      </c>
+      <c r="D19" t="n">
+        <v>18</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>-96.05763562375152</v>
+      </c>
+      <c r="I19" t="n">
+        <v>55.95491030000001</v>
+      </c>
+      <c r="J19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="b">
+        <v>1</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>45818.55005805555</v>
+      </c>
+      <c r="D20" t="n">
+        <v>19</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>-96.05763562375152</v>
+      </c>
+      <c r="I20" t="n">
+        <v>55.95491030000001</v>
+      </c>
+      <c r="J20" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="b">
+        <v>1</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>45818.55008127315</v>
+      </c>
+      <c r="D21" t="n">
+        <v>20</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>-96.05763562375152</v>
+      </c>
+      <c r="I21" t="n">
+        <v>55.95491030000001</v>
+      </c>
+      <c r="J21" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="b">
+        <v>1</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>45818.5529015625</v>
+      </c>
+      <c r="D22" t="n">
+        <v>21</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>-81.20838528789049</v>
+      </c>
+      <c r="I22" t="n">
+        <v>56.67382360000001</v>
+      </c>
+      <c r="J22" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="b">
+        <v>1</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>45818.55379043982</v>
+      </c>
+      <c r="D23" t="n">
+        <v>22</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>-81.20838528789049</v>
+      </c>
+      <c r="I23" t="n">
+        <v>56.67382360000001</v>
+      </c>
+      <c r="J23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="b">
+        <v>1</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>45818.55381290509</v>
+      </c>
+      <c r="D24" t="n">
+        <v>23</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>-81.20838528789049</v>
+      </c>
+      <c r="I24" t="n">
+        <v>56.67382360000001</v>
+      </c>
+      <c r="J24" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="b">
+        <v>1</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>45818.55792141204</v>
+      </c>
+      <c r="D25" t="n">
+        <v>24</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>-97.55982770572169</v>
+      </c>
+      <c r="I25" t="n">
+        <v>55.73406969999999</v>
+      </c>
+      <c r="J25" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="b">
+        <v>1</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>45818.55829056713</v>
+      </c>
+      <c r="D26" t="n">
+        <v>25</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>-97.55982770572169</v>
+      </c>
+      <c r="I26" t="n">
+        <v>55.73406969999999</v>
+      </c>
+      <c r="J26" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="b">
+        <v>1</v>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>45818.55831199074</v>
+      </c>
+      <c r="D27" t="n">
+        <v>26</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>-97.55982770572169</v>
+      </c>
+      <c r="I27" t="n">
+        <v>55.73406969999999</v>
+      </c>
+      <c r="J27" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="b">
+        <v>1</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>45818.55882462963</v>
+      </c>
+      <c r="D28" t="n">
+        <v>27</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>-97.55982770572169</v>
+      </c>
+      <c r="I28" t="n">
+        <v>55.73406969999999</v>
+      </c>
+      <c r="J28" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="b">
+        <v>1</v>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>45818.55884245371</v>
+      </c>
+      <c r="D29" t="n">
+        <v>28</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>-97.55982770572169</v>
+      </c>
+      <c r="I29" t="n">
+        <v>55.73406969999999</v>
+      </c>
+      <c r="J29" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="b">
+        <v>1</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>45818.5595853125</v>
+      </c>
+      <c r="D30" t="n">
+        <v>29</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>-97.55982770572169</v>
+      </c>
+      <c r="I30" t="n">
+        <v>55.73406969999999</v>
+      </c>
+      <c r="J30" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="b">
+        <v>1</v>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>45818.55960236111</v>
+      </c>
+      <c r="D31" t="n">
+        <v>30</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>-97.55982770572169</v>
+      </c>
+      <c r="I31" t="n">
+        <v>55.73406969999999</v>
+      </c>
+      <c r="J31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="b">
+        <v>1</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>45818.56010893518</v>
+      </c>
+      <c r="D32" t="n">
+        <v>31</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>-97.55982770572169</v>
+      </c>
+      <c r="I32" t="n">
+        <v>55.73406969999999</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="b">
+        <v>1</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>45818.56036958333</v>
+      </c>
+      <c r="D33" t="n">
+        <v>32</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>-97.55982770572169</v>
+      </c>
+      <c r="I33" t="n">
+        <v>55.73406969999999</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="b">
+        <v>1</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>45818.56043078704</v>
+      </c>
+      <c r="D34" t="n">
+        <v>33</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>-97.55982770572169</v>
+      </c>
+      <c r="I34" t="n">
+        <v>55.73406969999999</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="b">
+        <v>1</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>45818.56145732639</v>
+      </c>
+      <c r="D35" t="n">
+        <v>34</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>-97.55982770572169</v>
+      </c>
+      <c r="I35" t="n">
+        <v>55.73406969999999</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="b">
+        <v>1</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>45818.56151820602</v>
+      </c>
+      <c r="D36" t="n">
+        <v>35</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>-97.55982770572169</v>
+      </c>
+      <c r="I36" t="n">
+        <v>55.73406969999999</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1232</v>
       </c>
     </row>
   </sheetData>
@@ -727,7 +1483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1041,11 +1797,6 @@
       <c r="C9" t="n">
         <v>8</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
@@ -1054,15 +1805,11 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>3232</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>35545454656</t>
-        </is>
+      <c r="G9" t="n">
+        <v>3232</v>
+      </c>
+      <c r="H9" t="n">
+        <v>35545454656</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -1077,6 +1824,912 @@
         <v>120</v>
       </c>
       <c r="M9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>45818.52019158565</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>100</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>120</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>45818.52070096065</v>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>100</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>120</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>45818.52240875</v>
+      </c>
+      <c r="C12" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>100</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>120</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>45818.52286226852</v>
+      </c>
+      <c r="C13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>100</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>120</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>45818.52290732639</v>
+      </c>
+      <c r="C14" t="n">
+        <v>13</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>100</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>120</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>45818.52301774306</v>
+      </c>
+      <c r="C15" t="n">
+        <v>14</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>120</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>45818.52323211805</v>
+      </c>
+      <c r="C16" t="n">
+        <v>15</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>120</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>45818.53143945602</v>
+      </c>
+      <c r="C17" t="n">
+        <v>16</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>100</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>120</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>45818.54859282407</v>
+      </c>
+      <c r="C18" t="n">
+        <v>17</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>100</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>120</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>45818.54947380787</v>
+      </c>
+      <c r="C19" t="n">
+        <v>18</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>100</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>120</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>45818.55005805555</v>
+      </c>
+      <c r="C20" t="n">
+        <v>19</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>100</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>120</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>45818.55008127315</v>
+      </c>
+      <c r="C21" t="n">
+        <v>20</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>100</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>120</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>45818.5529015625</v>
+      </c>
+      <c r="C22" t="n">
+        <v>21</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>100</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>120</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>45818.55379043982</v>
+      </c>
+      <c r="C23" t="n">
+        <v>22</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>100</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>120</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>45818.55381290509</v>
+      </c>
+      <c r="C24" t="n">
+        <v>23</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>100</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>120</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>45818.55792141204</v>
+      </c>
+      <c r="C25" t="n">
+        <v>24</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>100</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>120</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>45818.55829056713</v>
+      </c>
+      <c r="C26" t="n">
+        <v>25</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>100</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L26" t="n">
+        <v>120</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>45818.55831199074</v>
+      </c>
+      <c r="C27" t="n">
+        <v>26</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>100</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L27" t="n">
+        <v>120</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>45818.55882462963</v>
+      </c>
+      <c r="C28" t="n">
+        <v>27</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>100</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L28" t="n">
+        <v>120</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>45818.55884245371</v>
+      </c>
+      <c r="C29" t="n">
+        <v>28</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>100</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>120</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>45818.5595853125</v>
+      </c>
+      <c r="C30" t="n">
+        <v>29</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>100</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L30" t="n">
+        <v>120</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>45818.55960236111</v>
+      </c>
+      <c r="C31" t="n">
+        <v>30</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>100</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>120</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>45818.56010893518</v>
+      </c>
+      <c r="C32" t="n">
+        <v>31</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1212</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>120</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>45818.56036958333</v>
+      </c>
+      <c r="C33" t="n">
+        <v>32</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1212</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L33" t="n">
+        <v>120</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>45818.56043078704</v>
+      </c>
+      <c r="C34" t="n">
+        <v>33</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L34" t="n">
+        <v>120</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>45818.56145732639</v>
+      </c>
+      <c r="C35" t="n">
+        <v>34</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L35" t="n">
+        <v>120</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>45818.56151820602</v>
+      </c>
+      <c r="C36" t="n">
+        <v>35</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>1232</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L36" t="n">
+        <v>120</v>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1093,7 +2746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1344,17 +2997,13 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>45817.56871664818</v>
+        <v>45817.56871664352</v>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>8</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
         <v>0</v>
       </c>
@@ -1372,6 +3021,739 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>45818.52019158565</v>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G10" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H10" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I10" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>45818.52070096065</v>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G11" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H11" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I11" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>45818.52240875</v>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G12" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I12" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>45818.52286226852</v>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G13" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I13" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>45818.52290732639</v>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G14" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I14" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>45818.52301774306</v>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>14</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G15" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H15" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I15" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>45818.52323211805</v>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G16" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H16" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I16" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>45818.53143945602</v>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>16</v>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G17" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I17" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>45818.54859282407</v>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="n">
+        <v>17</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G18" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I18" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>45818.54947380787</v>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>18</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G19" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H19" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I19" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>45818.55005805555</v>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>19</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G20" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I20" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>45818.55008127315</v>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="n">
+        <v>20</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G21" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I21" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>45818.5529015625</v>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="n">
+        <v>21</v>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G22" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H22" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I22" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>45818.55379043982</v>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="n">
+        <v>22</v>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G23" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I23" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>45818.55381290509</v>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="n">
+        <v>23</v>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G24" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I24" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>45818.55792141204</v>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="n">
+        <v>24</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G25" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H25" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I25" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>45818.55829056713</v>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="n">
+        <v>25</v>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G26" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H26" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I26" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>45818.55831199074</v>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="n">
+        <v>26</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G27" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I27" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>45818.55882462963</v>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="n">
+        <v>27</v>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G28" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I28" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>45818.55884245371</v>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="n">
+        <v>28</v>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G29" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I29" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>45818.5595853125</v>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="n">
+        <v>29</v>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G30" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I30" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>45818.55960236111</v>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="n">
+        <v>30</v>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G31" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I31" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>45818.56010893518</v>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="n">
+        <v>31</v>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G32" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H32" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I32" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>45818.56036958333</v>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="n">
+        <v>32</v>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G33" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H33" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I33" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>45818.56043078704</v>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="n">
+        <v>33</v>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G34" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H34" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I34" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>45818.56145732639</v>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="n">
+        <v>34</v>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G35" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I35" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>45818.56151821016</v>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="n">
+        <v>35</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>56.80026</v>
+      </c>
+      <c r="G36" t="n">
+        <v>57.29622609999999</v>
+      </c>
+      <c r="H36" t="n">
+        <v>57.97749800000003</v>
+      </c>
+      <c r="I36" t="n">
+        <v>59.50070250000001</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
